--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -1,33 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>BOSQUE</t>
+  </si>
+  <si>
+    <t>PRODUCTOS FRESCOS PROFRESCA, C.A</t>
+  </si>
+  <si>
+    <t>AGROPECUARIA PUNTA LARGA, C.A</t>
+  </si>
+  <si>
+    <t>AGROPECUARIA ORO BLANCO, C.A</t>
+  </si>
+  <si>
+    <t>6363</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>SUB MARIANGEL GRATEROL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB VICTOR SALCEDO </t>
+  </si>
+  <si>
+    <t>DOCUMENTACIÓN ERRÓNEA</t>
+  </si>
+  <si>
+    <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+  </si>
+  <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>ERROR EN EL DOCUMENTO, FECHA ESCRITA INCORRECTA</t>
+  </si>
+  <si>
+    <t>FALTA CEDULA DEL SPCP</t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504105230</t>
+  </si>
+  <si>
+    <t>20260504111753</t>
+  </si>
+  <si>
+    <t>20260504111902</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +149,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,144 +443,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BOSQUE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>003035</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUB VICTOR SALCEDO </t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIPO A</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>FALTA CÉDULA DEL SPCP</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>27959</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
         <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>3035</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>BOSQUE</t>
   </si>
   <si>
@@ -67,21 +70,33 @@
     <t>AGROPECUARIA ORO BLANCO, C.A</t>
   </si>
   <si>
-    <t>6363</t>
+    <t>RUBROS SANARE C2, C.A.</t>
+  </si>
+  <si>
+    <t>31909</t>
   </si>
   <si>
     <t>2026-05-01</t>
   </si>
   <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
+    <t>DEVOLUCION</t>
+  </si>
+  <si>
     <t>SUB MARIANGEL GRATEROL</t>
   </si>
   <si>
     <t xml:space="preserve">SUB VICTOR SALCEDO </t>
   </si>
   <si>
+    <t>PCP MOISES MORA</t>
+  </si>
+  <si>
     <t>DOCUMENTACIÓN ERRÓNEA</t>
   </si>
   <si>
@@ -100,19 +115,22 @@
     <t>FALTA CEDULA DEL SPCP</t>
   </si>
   <si>
+    <t>FALTA SELLO EN EL DOCUMENTO DE LA SUCURSAL</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
     <t>NINGUNA</t>
   </si>
   <si>
-    <t>20260504105230</t>
-  </si>
-  <si>
-    <t>20260504111753</t>
-  </si>
-  <si>
-    <t>20260504111902</t>
+    <t>ID_20260505092938</t>
+  </si>
+  <si>
+    <t>INC_093117.png</t>
   </si>
 </sst>
 </file>
@@ -444,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,128 +505,175 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>27959</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>20260504105230</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>3035</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
+        <v>20260504111753</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>6363</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4">
+        <v>20260504111902</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
       </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +616,6 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +677,6 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -786,7 +790,7 @@
           <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.76</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -804,7 +808,6 @@
           <t>ID_20260506082444</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -870,7 +873,6 @@
           <t>ID_20260506125441</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,65 +682,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RUBROS SANARE C2, C.A.</t>
+          <t>LA CARIDAD C.A.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31909</v>
+        <v>41798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PCP MOISES MORA</t>
+          <t>SUB SUGGEY CASTRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FALTA SELLO EN EL DOCUMENTO DE LA SUCURSAL</t>
+          <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>00320882.jpeg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260505092938</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>INC_093117.png</t>
-        </is>
-      </c>
+          <t>ID_20260506082444</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,11 +746,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA CARIDAD C.A.</t>
+          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41798</v>
+        <v>32104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -767,47 +759,48 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SUB SUGGEY CASTRO</t>
+          <t>SPCP LUISTER BOLIVAR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.76</v>
+          <t>FALTA SELLO DE SUCURSAL, NO COLOCÓ SELLO EN EL DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>00320882.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260506082444</t>
-        </is>
-      </c>
+          <t>ID_20260506125441</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -817,17 +810,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+          <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -837,7 +830,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SPCP LUISTER BOLIVAR</t>
+          <t>SPCP MOISES MORA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -852,7 +845,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FALTA SELLO DE SUCURSAL, NO COLOCÓ SELLO EN EL DOCUMENTO.</t>
+          <t>FALTA SELLO EN EL DOCUMENTO DE LA SUCURSAL</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -870,7 +863,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260506125441</t>
+          <t>ID_20260505092938</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_093117.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,10 +813,8 @@
           <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>31909</t>
-        </is>
+      <c r="C7" t="n">
+        <v>31909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -871,6 +869,192 @@
           <t>INC_093117.png</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FRUMIX,C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9619</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUB VIRGILIO ARAUJO </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SE VISUALIZA EXCEDENTE DE 6.2KG DE UVA VERDE EN RECEPCIÓN</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260507090852</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FRUMIX,C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9619</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUB VIRGILIO ARAUJO </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SE VISUALIZA EXCEDENTE DE 2.8KG DE UVA ROJA IMPORTADA</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260507091625</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>000906</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUB VIRGILIO ARAUJO </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ERROR EN SKU DE JOJOTO, INGRESA 8 CESTAS DE 2.6KG C/U, EN EL APLICATIVO. PRODUCTO SE FISCALIZA POR UNIDAD.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260507093401</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,10 +1001,8 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>000906</t>
-        </is>
+      <c r="C10" t="n">
+        <v>906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1055,6 +1053,72 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HELADOS EDMAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NO ESPECIFICADO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SPCP LUISTER BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NO CARGÓ DOCUMENTO A TIEMPO, RECEPCIÓN EN ESTADO DE "CARGADA"</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260508081314</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,6 +1119,208 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>32730</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SPCP LUISTER BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOCUMENTO CARGADO EN LA APP, NO PERTENECE A LA DEVOLUCIÓN </t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260508100340</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>32734</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SPCP LUISTER BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DOCUMENTO CARGADO EN LA APP, NO PERTENECE A LA DEVOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260508100058</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>32717</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SPCP LUISTER BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN FUERA DE VISUAL / CON OBSTRUCCIÓN.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DEVOLUCIÓN REALIZADA FUERA DE VISUAL, SIN CONTEO VISIBLE DE CADA PRODUCTO Y CON OBSTRUCCIÓN</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260508102050</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>INC_102118.jpeg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -26,12 +26,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +569,6 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +630,6 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +691,6 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -718,7 +736,7 @@
           <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.76</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -736,7 +754,6 @@
           <t>ID_20260506082444</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -800,7 +817,6 @@
           <t>ID_20260506125441</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -904,13 +920,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 6.2KG DE UVA VERDE EN RECEPCIÓN</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>72.78</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -928,7 +943,6 @@
           <t>ID_20260507090852</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -964,13 +978,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 2.8KG DE UVA ROJA IMPORTADA</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>19.51</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -988,7 +1001,6 @@
           <t>ID_20260507091625</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1052,7 +1064,6 @@
           <t>ID_20260507093401</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1118,7 +1129,6 @@
           <t>ID_20260508081314</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1184,7 +1194,6 @@
           <t>ID_20260508100340</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1250,7 +1259,6 @@
           <t>ID_20260508100058</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1368,7 +1376,7 @@
           <t>Error en tara de cedano, ingresó 230kg en tara, dando una diferencia de 207kg</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>186.3</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1386,7 +1394,6 @@
           <t>ID_20260508160942</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1452,7 +1459,6 @@
           <t>ID_20260511083454</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -71,7 +70,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -434,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,7 +1459,77 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>32997</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUB MOISES MORA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALTA SELLO DE SUCURSAL EN DOCUMENTO </t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ID_20260512094929</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>INC_094929.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,30 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -63,14 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -433,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -735,7 +718,7 @@
           <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="n">
         <v>0.76</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -753,6 +736,7 @@
           <t>ID_20260506082444</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -816,6 +800,7 @@
           <t>ID_20260506125441</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -919,12 +904,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 6.2KG DE UVA VERDE EN RECEPCIÓN</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>72.78</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -942,6 +928,7 @@
           <t>ID_20260507090852</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -977,12 +964,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 2.8KG DE UVA ROJA IMPORTADA</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>19.51</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -1000,6 +988,7 @@
           <t>ID_20260507091625</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1063,6 +1052,7 @@
           <t>ID_20260507093401</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,6 +1118,7 @@
           <t>ID_20260508081314</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1193,6 +1184,7 @@
           <t>ID_20260508100340</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1258,6 +1250,7 @@
           <t>ID_20260508100058</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1375,7 +1368,7 @@
           <t>Error en tara de cedano, ingresó 230kg en tara, dando una diferencia de 207kg</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" t="n">
         <v>186.3</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1393,6 +1386,7 @@
           <t>ID_20260508160942</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1458,6 +1452,7 @@
           <t>ID_20260511083454</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1529,7 +1524,73 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6008</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUB MARIANGEL GRATEROL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NO INGRESÓ UN SKU DE QUESO GUAYANES, CON TARA DE 4KG</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ID_20260512155936</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,6 +1590,76 @@
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PEPSI COLA VENEZUELA, C.A./S.T.C POLAR C.A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7343692540</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>INGRESA 1 UNIDAD DE REFRESCO PEPSI PET 2LTS AVERIADO, EL PROVEEDOR REALIZA EL PAGO DE LA MISMA</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>00163146.jpeg</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ID_20260513090328</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>INC_090328.jpeg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -26,12 +26,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +569,6 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +630,6 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +691,6 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -718,7 +736,7 @@
           <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.76</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -736,7 +754,6 @@
           <t>ID_20260506082444</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -800,7 +817,6 @@
           <t>ID_20260506125441</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -904,13 +920,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 6.2KG DE UVA VERDE EN RECEPCIÓN</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>72.78</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -928,7 +943,6 @@
           <t>ID_20260507090852</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -964,13 +978,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 2.8KG DE UVA ROJA IMPORTADA</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>19.51</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -988,7 +1001,6 @@
           <t>ID_20260507091625</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1052,7 +1064,6 @@
           <t>ID_20260507093401</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1118,7 +1129,6 @@
           <t>ID_20260508081314</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1184,7 +1194,6 @@
           <t>ID_20260508100340</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1250,7 +1259,6 @@
           <t>ID_20260508100058</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1368,7 +1376,7 @@
           <t>Error en tara de cedano, ingresó 230kg en tara, dando una diferencia de 207kg</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>186.3</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1386,7 +1394,6 @@
           <t>ID_20260508160942</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1452,7 +1459,6 @@
           <t>ID_20260511083454</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1588,7 +1594,6 @@
           <t>ID_20260512155936</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -26,30 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504105230</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -630,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504111753</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504111902</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -736,7 +718,7 @@
           <t>SE RECIBEN 99.9KG DE MOLLEJA DE POLLO, EN FACTURA 100.1KG. DIFERENCIA: 200GR FALTANTES</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="n">
         <v>0.76</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -754,6 +736,7 @@
           <t>ID_20260506082444</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +800,7 @@
           <t>ID_20260506125441</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -920,12 +904,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 6.2KG DE UVA VERDE EN RECEPCIÓN</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="n">
         <v>72.78</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -943,6 +928,7 @@
           <t>ID_20260507090852</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -978,12 +964,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>SE VISUALIZA EXCEDENTE DE 2.8KG DE UVA ROJA IMPORTADA</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" t="n">
         <v>19.51</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -1001,6 +988,7 @@
           <t>ID_20260507091625</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1064,6 +1052,7 @@
           <t>ID_20260507093401</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1129,6 +1118,7 @@
           <t>ID_20260508081314</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1194,6 +1184,7 @@
           <t>ID_20260508100340</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1259,6 +1250,7 @@
           <t>ID_20260508100058</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1376,7 +1368,7 @@
           <t>Error en tara de cedano, ingresó 230kg en tara, dando una diferencia de 207kg</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" t="n">
         <v>186.3</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1394,6 +1386,7 @@
           <t>ID_20260508160942</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1459,6 +1452,7 @@
           <t>ID_20260511083454</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1594,6 +1588,7 @@
           <t>ID_20260512155936</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1631,11 +1626,7 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>INGRESA 1 UNIDAD DE REFRESCO PEPSI PET 2LTS AVERIADO, EL PROVEEDOR REALIZA EL PAGO DE LA MISMA</t>
@@ -1664,6 +1655,72 @@
           <t>INC_090328.jpeg</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ECO CARNES, C.A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>000510</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SUB VICTOR SALCEDO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGRESA SKU DE CERDO EN CANAL S/ CUERO,  A DESTIEMPO DE LA FISCALIZACIÓN </t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ID_20260513103845</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,6 +1722,76 @@
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13660</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SUB MARIANGEL GRATEROL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE NO INGRESÓ 2 CESTAS DE 2.3KG C/U EN SKU DE ALBAHACA, 4.6KG </t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SIN_FOTO.png</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ID_20260513152631</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>INC_152631.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,8 +519,10 @@
           <t>PRODUCTOS FRESCOS PROFRESCA, C.A</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>27959</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>27959</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -580,8 +582,10 @@
           <t>AGROPECUARIA PUNTA LARGA, C.A</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>3035</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -641,8 +645,10 @@
           <t>AGROPECUARIA ORO BLANCO, C.A</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>6363</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6363</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -702,8 +708,10 @@
           <t>LA CARIDAD C.A.</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>41798</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>41798</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -765,8 +773,10 @@
           <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>32104</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>32104</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -828,8 +838,10 @@
           <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>31909</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>31909</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -896,8 +908,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>906</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1945,6 +1959,76 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>ID_20260514101038</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VISA FOODS, C.A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>33813</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SUB LADY PORTES</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NO CULMINÓ A TIEMPO EL PROCESO DE FISCALIZACIÓN, DEJANDO LA RECEPCIÓN EN ESTADO "CARGADA"</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ID_20260515073821</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>INC_073821_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2032,6 +2032,71 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA ORO BLANCO, C.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>006379</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SUB VIRGILIO ARAUJO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL INGRESADO EN LA APP ES INCORRECTO. NÚMERO DE CONTROL CORRECTO: 00-006379</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ID_20260515160718</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cuadros/MAYO/BOSQUE.xlsx
+++ b/cuadros/MAYO/BOSQUE.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,6 +2097,72 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>YEFFERSON MAY MORGADO CHACON</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>126259</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VIRGILIO A. ARAUJO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE INICIA RECEPCIÓN SIN PREVIA AUTORIZACIÓN _x000D_
+</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ID_20260515161839</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
